--- a/BOM Format/PCBWay.Bom.Template.xlsx
+++ b/BOM Format/PCBWay.Bom.Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FDEA03-A15D-4875-99A5-02C005008651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1463F209-D0FA-4AED-83F2-F4232447B1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -217,7 +217,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -238,12 +238,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -472,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -546,13 +540,13 @@
     <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -577,12 +571,6 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -590,9 +578,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -629,7 +614,7 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1007,16 +992,16 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
     </row>
     <row r="2" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="23"/>
-      <c r="C2" s="52"/>
+      <c r="C2" s="49"/>
       <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
@@ -1031,12 +1016,12 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
-      <c r="N2" s="49"/>
+      <c r="N2" s="46"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="24"/>
-      <c r="C3" s="53"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="12" t="s">
         <v>2</v>
       </c>
@@ -1051,12 +1036,12 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="61"/>
+      <c r="N3" s="58"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="24"/>
-      <c r="C4" s="53"/>
+      <c r="C4" s="50"/>
       <c r="D4" s="12" t="s">
         <v>4</v>
       </c>
@@ -1071,12 +1056,12 @@
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
-      <c r="N4" s="62"/>
+      <c r="N4" s="59"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="24"/>
-      <c r="C5" s="53"/>
+      <c r="C5" s="50"/>
       <c r="D5" s="12" t="s">
         <v>6</v>
       </c>
@@ -1091,12 +1076,12 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="62"/>
+      <c r="N5" s="59"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="25"/>
-      <c r="C6" s="54"/>
+      <c r="C6" s="51"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
@@ -1107,12 +1092,12 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
-      <c r="N6" s="62"/>
+      <c r="N6" s="59"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="26"/>
-      <c r="C7" s="55"/>
+      <c r="C7" s="52"/>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="F7" s="21"/>
@@ -1123,12 +1108,12 @@
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
-      <c r="N7" s="62"/>
+      <c r="N7" s="59"/>
     </row>
     <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="29"/>
-      <c r="C8" s="56"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
       <c r="F8" s="31"/>
@@ -1139,7 +1124,7 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
-      <c r="N8" s="62"/>
+      <c r="N8" s="59"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1185,7 +1170,7 @@
     </row>
     <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="59">
+      <c r="B10" s="56">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
@@ -1200,11 +1185,11 @@
       <c r="K10" s="40"/>
       <c r="L10" s="40"/>
       <c r="M10" s="40"/>
-      <c r="N10" s="46"/>
+      <c r="N10" s="44"/>
     </row>
     <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="59">
+      <c r="B11" s="56">
         <f t="shared" ref="B11:B12" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
@@ -1219,31 +1204,31 @@
       <c r="K11" s="42"/>
       <c r="L11" s="42"/>
       <c r="M11" s="42"/>
-      <c r="N11" s="47"/>
+      <c r="N11" s="45"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="59">
+      <c r="B12" s="56">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C12" s="40"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="44"/>
-      <c r="N12" s="48"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="45"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="35"/>
-      <c r="C13" s="57"/>
+      <c r="C13" s="54"/>
       <c r="D13" s="36"/>
       <c r="E13" s="37"/>
       <c r="F13" s="38"/>
@@ -1254,12 +1239,12 @@
       <c r="K13" s="39"/>
       <c r="L13" s="39"/>
       <c r="M13" s="39"/>
-      <c r="N13" s="50"/>
+      <c r="N13" s="47"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="58"/>
+      <c r="C14" s="55"/>
       <c r="D14" s="8"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
@@ -1270,7 +1255,7 @@
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
-      <c r="N14" s="51"/>
+      <c r="N14" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="2">
